--- a/artfynd/A 8857-2024 artfynd.xlsx
+++ b/artfynd/A 8857-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135363784</v>
+        <v>135363194</v>
       </c>
       <c r="B2" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631485</v>
+        <v>631544</v>
       </c>
       <c r="R2" t="n">
-        <v>6990938</v>
+        <v>6990940</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,15 +778,615 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135363199</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Storklacken, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>631546</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6990969</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135363200</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storklacken, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>631552</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6990968</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135363217</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storklacken, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>631521</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6990911</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135363784</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storklacken, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>631485</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6990938</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Ann-Christine Borja</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Ann-Christine Borja</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135363193</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storklacken, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>631527</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6990919</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8857-2024 artfynd.xlsx
+++ b/artfynd/A 8857-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135363194</v>
+        <v>135363784</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>57162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631544</v>
+        <v>631485</v>
       </c>
       <c r="R2" t="n">
-        <v>6990940</v>
+        <v>6990938</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,615 +778,15 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>135363199</v>
-      </c>
-      <c r="B3" t="n">
-        <v>57972</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Storklacken, Ång</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>631546</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6990969</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Ytterlännäs</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>135363200</v>
-      </c>
-      <c r="B4" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Storklacken, Ång</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>631552</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6990968</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Ytterlännäs</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>135363217</v>
-      </c>
-      <c r="B5" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Storklacken, Ång</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>631521</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6990911</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Ytterlännäs</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:16</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:16</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>135363784</v>
-      </c>
-      <c r="B6" t="n">
-        <v>57162</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Storklacken, Ång</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>631485</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6990938</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Ytterlännäs</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>135363193</v>
-      </c>
-      <c r="B7" t="n">
-        <v>58136</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Storklacken, Ång</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>631527</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6990919</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Ytterlännäs</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8857-2024 artfynd.xlsx
+++ b/artfynd/A 8857-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,13 +672,18 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135363194</v>
+        <v>135363784</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>57162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -708,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631544</v>
+        <v>631485</v>
       </c>
       <c r="R2" t="n">
-        <v>6990940</v>
+        <v>6990938</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,617 +783,25 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>135363199</v>
-      </c>
-      <c r="B3" t="n">
-        <v>57972</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Storklacken, Ång</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>631546</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6990969</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Ytterlännäs</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>135363200</v>
-      </c>
-      <c r="B4" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Storklacken, Ång</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>631552</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6990968</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Ytterlännäs</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>135363217</v>
-      </c>
-      <c r="B5" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Storklacken, Ång</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>631521</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6990911</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Ytterlännäs</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:16</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:16</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>135363784</v>
-      </c>
-      <c r="B6" t="n">
-        <v>57162</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Storklacken, Ång</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>631485</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6990938</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Ytterlännäs</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>135363193</v>
-      </c>
-      <c r="B7" t="n">
-        <v>58136</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Storklacken, Ång</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>631527</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6990919</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Ytterlännäs</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363784</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 8857-2024 artfynd.xlsx
+++ b/artfynd/A 8857-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135363784</v>
+        <v>135363194</v>
       </c>
       <c r="B2" t="n">
-        <v>57162</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631485</v>
+        <v>631544</v>
       </c>
       <c r="R2" t="n">
-        <v>6990938</v>
+        <v>6990940</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,24 +783,654 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135363194</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135363199</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Storklacken, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>631546</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6990969</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363199</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135363200</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storklacken, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>631552</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6990968</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363200</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135363217</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storklacken, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>631521</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6990911</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363217</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135363784</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storklacken, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>631485</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6990938</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135363784</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135363193</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storklacken, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>631527</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6990919</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363193</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8857-2024 artfynd.xlsx
+++ b/artfynd/A 8857-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135363194</v>
+        <v>135363784</v>
       </c>
       <c r="B2" t="n">
-        <v>57977</v>
+        <v>57167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631544</v>
+        <v>631485</v>
       </c>
       <c r="R2" t="n">
-        <v>6990940</v>
+        <v>6990938</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,654 +783,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135363194</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>135363199</v>
-      </c>
-      <c r="B3" t="n">
-        <v>57977</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Storklacken, Ång</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>631546</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6990969</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Ytterlännäs</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135363199</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>135363200</v>
-      </c>
-      <c r="B4" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Storklacken, Ång</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>631552</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6990968</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Ytterlännäs</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135363200</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>135363217</v>
-      </c>
-      <c r="B5" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Storklacken, Ång</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>631521</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6990911</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Ytterlännäs</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:16</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:16</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135363217</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>135363784</v>
-      </c>
-      <c r="B6" t="n">
-        <v>57167</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Storklacken, Ång</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>631485</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6990938</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Ytterlännäs</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/135363784</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>135363193</v>
-      </c>
-      <c r="B7" t="n">
-        <v>58141</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Storklacken, Ång</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>631527</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6990919</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Ytterlännäs</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135363193</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8857-2024 artfynd.xlsx
+++ b/artfynd/A 8857-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135363784</v>
+        <v>135363194</v>
       </c>
       <c r="B2" t="n">
-        <v>57167</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631485</v>
+        <v>631544</v>
       </c>
       <c r="R2" t="n">
-        <v>6990938</v>
+        <v>6990940</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,24 +783,654 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135363194</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135363199</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Storklacken, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>631546</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6990969</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363199</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135363200</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storklacken, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>631552</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6990968</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363200</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135363217</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storklacken, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>631521</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6990911</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363217</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135363784</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storklacken, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>631485</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6990938</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135363784</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135363193</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storklacken, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>631527</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6990919</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363193</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
